--- a/test_pn.xlsx
+++ b/test_pn.xlsx
@@ -356,10 +356,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -373,21 +388,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -677,106 +677,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="S1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="U1" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="W1" s="10"/>
-      <c r="X1" s="11" t="s">
+      <c r="W1" s="8"/>
+      <c r="X1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:24" s="1" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
       <c r="V2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="W2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="X2" s="12"/>
+      <c r="X2" s="5"/>
     </row>
     <row r="3" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1355,7 +1355,7 @@
         <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
@@ -2183,17 +2183,6 @@
     <filterColumn colId="21" showButton="0"/>
   </autoFilter>
   <mergeCells count="23">
-    <mergeCell ref="X1:X2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="T1:T2"/>
-    <mergeCell ref="U1:U2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
@@ -2206,6 +2195,17 @@
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
+    <mergeCell ref="X1:X2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="T1:T2"/>
+    <mergeCell ref="U1:U2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
